--- a/ExcelToJSONConverter/excel/dailyDungeon.xlsx
+++ b/ExcelToJSONConverter/excel/dailyDungeon.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A4D5C0-2190-4979-8A59-9A6EC8DF11BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820933C7-298E-4106-9C8A-0F39F88CBF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="DailyDungeonGrade" sheetId="8" r:id="rId2"/>
-    <sheet name="DailyDungeonBoss" sheetId="6" r:id="rId3"/>
+    <sheet name="s_daily_dungeon_grade" sheetId="8" r:id="rId2"/>
+    <sheet name="s_daily_dungeon_boss" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -730,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
@@ -791,43 +791,43 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B16">
+      <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B18">
+      <c r="B12">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B20">
+      <c r="B14">
         <v>4</v>
       </c>
     </row>
@@ -927,7 +927,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="5">
-        <f>VLOOKUP(B3,Overview!A16:B20,2,FALSE)</f>
+        <f>VLOOKUP(B3,Overview!A10:B14,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="D3" s="5">
@@ -960,7 +960,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="5">
-        <f>VLOOKUP(B4,Overview!A17:B21,2,FALSE)</f>
+        <f>VLOOKUP(B4,Overview!A11:B21,2,FALSE)</f>
         <v>1</v>
       </c>
       <c r="D4" s="5">
@@ -993,7 +993,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="5">
-        <f>VLOOKUP(B5,Overview!A18:B22,2,FALSE)</f>
+        <f>VLOOKUP(B5,Overview!A12:B22,2,FALSE)</f>
         <v>2</v>
       </c>
       <c r="D5" s="5">
@@ -1026,7 +1026,7 @@
         <v>29</v>
       </c>
       <c r="C6" s="5">
-        <f>VLOOKUP(B6,Overview!A19:B23,2,FALSE)</f>
+        <f>VLOOKUP(B6,Overview!A13:B23,2,FALSE)</f>
         <v>3</v>
       </c>
       <c r="D6" s="5">
@@ -1059,7 +1059,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <f>VLOOKUP(B7,Overview!A20:B24,2,FALSE)</f>
+        <f>VLOOKUP(B7,Overview!A14:B24,2,FALSE)</f>
         <v>4</v>
       </c>
       <c r="D7" s="5">
@@ -1218,7 +1218,7 @@
         <v>43</v>
       </c>
       <c r="D6" s="9">
-        <f>VLOOKUP(C6,Overview!A5:B10,2,FALSE)</f>
+        <f>VLOOKUP(C6,Overview!A5:B9,2,FALSE)</f>
         <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1239,7 +1239,7 @@
         <v>47</v>
       </c>
       <c r="D7" s="9">
-        <f>VLOOKUP(C7,Overview!A6:B11,2,FALSE)</f>
+        <f>VLOOKUP(C7,Overview!A6:B9,2,FALSE)</f>
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1260,7 +1260,7 @@
         <v>51</v>
       </c>
       <c r="D8" s="9">
-        <f>VLOOKUP(C8,Overview!A7:B12,2,FALSE)</f>
+        <f>VLOOKUP(C8,Overview!A7:B9,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="E8" s="3" t="s">
